--- a/03_Group_comparisons/Muscle_strength/c_data/05_module_classification.xlsx
+++ b/03_Group_comparisons/Muscle_strength/c_data/05_module_classification.xlsx
@@ -223,34 +223,34 @@
     <t>Where the package came from.</t>
   </si>
   <si>
-    <t>Baseline_HivLo</t>
-  </si>
-  <si>
-    <t>Hi vs Lo at T1</t>
-  </si>
-  <si>
-    <t>Trained_HivLo</t>
-  </si>
-  <si>
-    <t>Hi vs Lo at T2</t>
-  </si>
-  <si>
-    <t>Acute_HivLo</t>
-  </si>
-  <si>
-    <t>Hi vs Lo at T3</t>
-  </si>
-  <si>
-    <t>Training_change_HivLo</t>
-  </si>
-  <si>
-    <t>Hi vs Lo, training change</t>
-  </si>
-  <si>
-    <t>Acute_change_HivLo</t>
-  </si>
-  <si>
-    <t>Hi vs Lo, acute change</t>
+    <t>Baseline_HRvLR</t>
+  </si>
+  <si>
+    <t>HR vs LR at T1</t>
+  </si>
+  <si>
+    <t>Trained_HRvLR</t>
+  </si>
+  <si>
+    <t>HR vs LR at T2</t>
+  </si>
+  <si>
+    <t>Acute_HRvLR</t>
+  </si>
+  <si>
+    <t>HR vs LR at T3</t>
+  </si>
+  <si>
+    <t>Training_change_HRvLR</t>
+  </si>
+  <si>
+    <t>HR vs LR, training change</t>
+  </si>
+  <si>
+    <t>Acute_change_HRvLR</t>
+  </si>
+  <si>
+    <t>HR vs LR, acute change</t>
   </si>
   <si>
     <t>blue</t>
@@ -310,7 +310,7 @@
     <t>03_Group_comparisons/Muscle_strength/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>c0cfb05785ba25feadb966caf1fa5a50</t>
+    <t>daa25e602fb59296ec25b2509cc40908</t>
   </si>
   <si>
     <t>modules</t>
@@ -319,7 +319,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
+    <t>37335a295505b53dcf355baf87333202</t>
   </si>
   <si>
     <t>BiocGenerics</t>
